--- a/results/workbooks/TOEV_MASTER_DERIVATION_LEDGER.xlsx
+++ b/results/workbooks/TOEV_MASTER_DERIVATION_LEDGER.xlsx
@@ -726,13 +726,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16.2" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="34.2" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -930,6 +930,50 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>CERTIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LEMMA-AUT-PROJ-001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Graph automorphisms commute with every spectral projector of L (incl. P_ker(L) and exp(-tL))</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>P A P^T=A (automorphism) =&gt; P D P^T=D =&gt; PL=LP =&gt; P preserves every eigenspace of L. Standard linear algebra, general proof + verified 9/9 benchmark families (max err 3.9e-16). Proof: proofs/C0/PRF-PRIM/LEMMA_automorphism_commutes_with_spectral_projector.md. Derived in PRF-PRIM-EXEC-2026-08-17 while testing candidate kappa=P_ker(L), tau=automorphism (PRF-PRIM).</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CERTIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LEMMA-INC-001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>L = Inc * Inc^T for the oriented incidence matrix Inc of any graph</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Standard algebraic graph theory (Godsil &amp; Royle Ch.13); ADMITTED EXTERNAL INPUT EXT-001. Verified exactly (sympy integer arithmetic) on 9/9 benchmark families. Proof: proofs/C0/PRF-PRIM/LEMMA_L_equals_incidence_incidence_transpose.md. Applied in PRF-PRIM-EXEC-2026-08-17 while testing candidate grad(Phi)&lt;-&gt;Delta structural correspondence (PRF-PRIM).</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CERTIFIED (external theorem, admitted)</t>
         </is>
       </c>
     </row>
@@ -944,11 +988,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22.5" customWidth="1" min="2" max="2"/>
+    <col width="24.3" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="21.6" customWidth="1" min="4" max="4"/>
   </cols>
@@ -1258,6 +1302,94 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-TAU-REALIZATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Which realization of tau (PRIM-G-002/PRIM-X-002) is intended</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17 tested 2 candidates: graph automorphism (satisfies tau's own Liouville-condition definition, 9/9) vs. diffusion semigroup exp(-tL) (FALSIFIES the same definition, 9/9). Source does not specify which. Neither proven to be the unique intended realization.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PRF-PRIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-DELTA-TYPE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Type-theoretic reconciliation of Delta's two source formulations</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17 showed PRIM-G-001's literal formula (boundary operator, d^2=0, a map between DIFFERENT graded spaces C_1-&gt;C_0) is type-incompatible with DER-ORG-002's required usage (an endomorphism X-&gt;X for Psi_(t+1)=kappa(tau(Delta(Psi_t))) to be iterable). Demonstrated concretely on the K4 tetrahedron complex (derivations/C0/PRF-PRIM/05_composition_type_check.py). Missing: an explicit reconciled definition of Delta that satisfies both roles, or an explanation of why they need not agree.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PRF-PRIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-OMEGA-PSI-IDENTITY</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Whether Omega (PRIM-X-006, Organizational State) is the same object as Psi (grammar A's state variable, DER-ORG-002)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17 found no computation or recovered source text (Combined Compiler Theories Whitepaper para. 550-553 asserts Omega has 'its own evolution law and variational structure' but the exact functional form was not present in the extracted text corpus available to this session) that distinguishes Omega from Psi as a different type of object. Not merged by assumption.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PRF-PRIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-PRIMC-LINK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>How PRIM-C-001 (B=(U,V,E), Computational realization) relates to grammars A, B, or D</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17 found ZERO tested computation or source-documented correspondence between PRIM-C-001 and any primitive in A/B/D. The corpus's own downstream pipeline (DER-SPC-001 'Graph G=(V,E)') is sourced from DER-ORG-001, not from PRIM-C-001, suggesting PRIM-C may not actually be used downstream despite being registered. Missing: either a constructive link or an explicit admission that PRIM-C is currently disconnected from the rest of the architecture.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PRF-PRIM</t>
         </is>
       </c>
     </row>
@@ -1272,19 +1404,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.6" customWidth="1" min="1" max="1"/>
-    <col width="17.1" customWidth="1" min="2" max="2"/>
-    <col width="30.6" customWidth="1" min="3" max="3"/>
-    <col width="38.7" customWidth="1" min="4" max="4"/>
-    <col width="26.1" customWidth="1" min="5" max="5"/>
-    <col width="44.1" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="1" max="1"/>
+    <col width="31.5" customWidth="1" min="2" max="2"/>
+    <col width="35.1" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="31.5" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="15.3" customWidth="1" min="7" max="7"/>
     <col width="12.6" customWidth="1" min="8" max="8"/>
     <col width="15.3" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2730,6 +2862,161 @@
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BR-PRF-PRIM-001</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>kappa[A/D] -&gt; P_ker(L)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Constraint-to-spectral-projector bridge</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>kappa candidate realized as idempotent spectral projector onto ker(L)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CANDIDATE, SURVIVES 9/9</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>commutes exactly with tau=automorphism (proven+verified)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>UNADJUDICATED</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CANDIDATE</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Falsified if a graph found where P_ker(L)^2 != P_ker(L) beyond float tolerance (none found, 9/9; theoretically impossible by spectral theorem)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BR-PRF-PRIM-002</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pi[A/D] -&gt; ker(L)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Persistence-to-kernel bridge</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pi = im(kappa) once kappa=P_ker(L)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CANDIDATE, SURVIVES (derivable) 9/9</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>consistent with DER-SPC-005 naming R=exp(-beta L) the persistence operator</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>UNADJUDICATED</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>CANDIDATE</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Falsified if lim_(t-&gt;inf) exp(-tL) != P_ker(L) for some graph (none found, 9/9; theoretically guaranteed by spectral theorem for connected-component structure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BR-PRF-PRIM-003</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Theta[D] -&gt; reachability-classes(G)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Accessibility-to-connectivity bridge</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Theta's reachability structure coincides with connected-component partition</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CALCULATED, SURVIVES 9/9</t>
+        </is>
+      </c>
+      <c r="F33">
+        <f> N - rank(L) = dim ker(L)</f>
+        <v/>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>UNADJUDICATED</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>CANDIDATE</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Falsified if a graph found where reachability-class count != connected-component count (none found, 9/9; theoretically guaranteed for undirected graphs)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4980,7 +5267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5646,229 +5933,204 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>tau realized as diffusion semigroup exp(-tL)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>N/A -- ruled out as a candidate realization of tau</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NO-GO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17: violates tau's own Liouville-condition definition on 9/9 benchmark families (FALS-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Delta realized as I-P_ker(L) endomorphism, composed as kappa o tau o Delta</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>N/A -- ruled out</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NO-GO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17: composition degenerates to the identically-zero map on 9/9 families (FALS-002)</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>SEIT open work &amp; falsification</t>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gamma_graph (graph-spectral realization) conjugate to exp(-hL) via orthogonal transform</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>A different conjugacy criterion or realization, if one exists</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NO-GO (for tested criterion)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17: no near-conjugacy found on 9/9 families, Procrustes residuals 0.88-0.97 (FALS-003)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>Priority / ID</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>Dependency</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>Test / Method</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>Failure or Closure Condition</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>Current Status</t>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Delta reconstructible from tau(automorphism)+kappa(spectrum) alone</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>N/A -- ruled out by external theorem</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NO-GO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17: cospectral non-isomorphic graphs are a standard counterexample (FALS-004, EXT-002)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEIT-1</t>
+          <t>C0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Evaluate Γ projection integral</t>
+          <t>Common minimal grammar Gamma_min across all 4 registered primitive systems (A,B,C,D)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C_Π</t>
+          <t>A tested structure-preserving embedding from each of A,B,C,D into a single candidate</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Compute restoring and higher-mode projections</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Finite computable Γ</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>SEIT-2</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Prove Γ strictly decreasing</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>SEIT-1</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Monotonicity proof</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Unique λ_c</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>SEIT-3</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Derive λ_c(β)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>SEIT-1/2</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Root flow in β</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RG-consistent running threshold</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>PRF-PRIM-EXEC-2026-08-17: not established; closest result is a 3-slot reduction WITHIN grammar A/D alone (Delta,tau-slot,kappa), not a 4-grammar unification. See Common_Grammar sheet, results/workbooks/C0_PRF_PRIM_Primitive_Reconciliation.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>SEIT-4</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Derive P_k</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>λ_c</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Locate UTT slope transitions</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Projectors derived</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>SEIT open work &amp; falsification</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>SEIT-5</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Normalize m0</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>λ_c Planck</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Unit audit</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>No free mass normalization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Priority / ID</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>Test / Method</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>Failure or Closure Condition</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>Current Status</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEIT-6</t>
+          <t>SEIT-1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Derive force count=3</t>
+          <t>Evaluate Γ projection integral</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>P_k</t>
+          <t>C_Π</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Prove two transitions</t>
+          <t>Compute restoring and higher-mode projections</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Three sectors forced</t>
+          <t>Finite computable Γ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5880,27 +6142,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEIT-7</t>
+          <t>SEIT-2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Derive gauge group</t>
+          <t>Prove Γ strictly decreasing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Graph Clifford structure</t>
+          <t>SEIT-1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Select SM group and rule out alternatives</t>
+          <t>Monotonicity proof</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Unique SU(3)×SU(2)×U(1)</t>
+          <t>Unique λ_c</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5912,27 +6174,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEIT-8</t>
+          <t>SEIT-3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Close N_sub</t>
+          <t>Derive λ_c(β)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spectral dimension</t>
+          <t>SEIT-1/2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hubble-radius derivation</t>
+          <t>Root flow in β</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Independent n_s derivation</t>
+          <t>RG-consistent running threshold</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5944,27 +6206,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEIT-9</t>
+          <t>SEIT-4</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Classify empirical inputs</t>
+          <t>Derive P_k</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>All closure</t>
+          <t>λ_c</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Input audit</t>
+          <t>Locate UTT slope transitions</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>External/derived partition</t>
+          <t>Projectors derived</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5976,315 +6238,315 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>F-1</t>
+          <t>SEIT-5</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>UV photon delay</t>
+          <t>Normalize m0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spectral d'Alembertian</t>
+          <t>λ_c Planck</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Gamma-ray time-of-flight</t>
+          <t>Unit audit</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Observed delay absent / wrong scaling</t>
+          <t>No free mass normalization</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>F-2</t>
+          <t>SEIT-6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IR lensing</t>
+          <t>Derive force count=3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Graph Green function</t>
+          <t>P_k</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Weak-lensing profile</t>
+          <t>Prove two transitions</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Profile fails quantitative test</t>
+          <t>Three sectors forced</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>F-3</t>
+          <t>SEIT-7</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Quantum metric noise</t>
+          <t>Derive gauge group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Discrete metric model</t>
+          <t>Graph Clifford structure</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GW interferometer spectrum</t>
+          <t>Select SM group and rule out alternatives</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Noise floor absent / wrong scaling</t>
+          <t>Unique SU(3)×SU(2)×U(1)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>F-4</t>
+          <t>SEIT-8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Graph reconstruction</t>
+          <t>Close N_sub</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Inverse spectral map</t>
+          <t>Spectral dimension</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Algorithmic reconstruction</t>
+          <t>Hubble-radius derivation</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Known undecidability boundary</t>
+          <t>Independent n_s derivation</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Undecidable</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>P-I</t>
+          <t>SEIT-9</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dimensional explosion</t>
+          <t>Classify empirical inputs</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Refinement R</t>
+          <t>All closure</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>lim max deg(v)=∞</t>
+          <t>Input audit</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Falsifies continuum dimension stability</t>
+          <t>External/derived partition</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>P-II</t>
+          <t>F-1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cochain rupture</t>
+          <t>UV photon delay</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chain map</t>
+          <t>Spectral d'Alembertian</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>dR≠Rd</t>
+          <t>Gamma-ray time-of-flight</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Falsifies discrete differential complex</t>
+          <t>Observed delay absent / wrong scaling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Partial</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>P-III</t>
+          <t>F-2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Metric asymmetry</t>
+          <t>IR lensing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hodge star</t>
+          <t>Graph Green function</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>⋆R≠scaled R⋆</t>
+          <t>Weak-lensing profile</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Falsifies self-adjoint spectral geometry</t>
+          <t>Profile fails quantitative test</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Partial</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>P-IV</t>
+          <t>F-3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Optimizer instability</t>
+          <t>Quantum metric noise</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Step size</t>
+          <t>Discrete metric model</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>β≥2/Λmax</t>
+          <t>GW interferometer spectrum</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Falsifies convergence</t>
+          <t>Noise floor absent / wrong scaling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Partial</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>P-V</t>
+          <t>F-4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Attractor fragmentation</t>
+          <t>Graph reconstruction</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Convexity</t>
+          <t>Inverse spectral map</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>λmin(H)≤0</t>
+          <t>Algorithmic reconstruction</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Falsifies unique attractor</t>
+          <t>Known undecidability boundary</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Undecidable</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>P-VI</t>
+          <t>P-I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Loss of precompactness</t>
+          <t>Dimensional explosion</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GH/doubling</t>
+          <t>Refinement R</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>lim C_n=∞</t>
+          <t>lim max deg(v)=∞</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Falsifies smooth continuum limit</t>
+          <t>Falsifies continuum dimension stability</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6296,27 +6558,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>P-VII</t>
+          <t>P-II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Torsion singularity</t>
+          <t>Cochain rupture</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Weitzenböck</t>
+          <t>Chain map</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Commutator identity fails</t>
+          <t>dR≠Rd</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Falsifies intended GR limit</t>
+          <t>Falsifies discrete differential complex</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6328,30 +6590,190 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>P-III</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Metric asymmetry</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Hodge star</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>⋆R≠scaled R⋆</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Falsifies self-adjoint spectral geometry</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P-IV</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Optimizer instability</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Step size</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>β≥2/Λmax</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Falsifies convergence</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P-V</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Attractor fragmentation</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Convexity</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>λmin(H)≤0</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Falsifies unique attractor</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P-VI</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Loss of precompactness</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GH/doubling</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>lim C_n=∞</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Falsifies smooth continuum limit</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P-VII</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Torsion singularity</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Weitzenböck</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Commutator identity fails</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Falsifies intended GR limit</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>P-VIII</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Index shattering</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Fredholm stability</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Infinite zero crossings</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Falsifies topological stability</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Diagnostic</t>
         </is>
@@ -6368,18 +6790,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J386"/>
+  <dimension ref="A1:J391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="21.6" customWidth="1" min="2" max="2"/>
     <col width="20.7" customWidth="1" min="3" max="3"/>
     <col width="19.8" customWidth="1" min="4" max="4"/>
-    <col width="41.4" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="26.1" customWidth="1" min="6" max="6"/>
     <col width="21.6" customWidth="1" min="7" max="7"/>
     <col width="44.1" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="39.6" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -22150,6 +22572,225 @@
         </is>
       </c>
       <c r="I386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>EDGE-PRF-PRIM-001</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>PROOF_DEPENDENCY</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>PRF-PRIM</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>DER-C0-PRIMGRAPH-001</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>This execution's computational test targets PRF-PRIM</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>graph-spectral realization only</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>EDGE-PRF-PRIM-002</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>DERIVED_FROM</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>DER-C0-PRIMGRAPH-001</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>LEMMA-AUT-PROJ-001</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Commutation lemma proven while testing kappa=P_ker(L), tau=automorphism candidates</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>CERTIFIED</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>graph automorphisms only</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>EDGE-PRF-PRIM-003</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>DERIVED_FROM</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>DER-C0-PRIMGRAPH-001</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>LEMMA-INC-001</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Incidence identity applied while testing grad(Phi)&lt;-&gt;Delta structural correspondence</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>CERTIFIED</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>any finite graph</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>EDGE-PRF-PRIM-004</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>TESTED_AGAINST</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>DER-C0-PRIMGRAPH-001</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>DER-SPC-005</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Candidate kappa=P_ker(L),Pi=ker(L) tested for compatibility with existing 'Persistence operator R=exp(-beta L)'; COMPATIBLE (lim R(t)=P_ker(L) verified 9/9)</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>9 benchmark graph families</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>EDGE-PRF-PRIM-005</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>FALSIFIES</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>DER-C0-PRIMGRAPH-001</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>PRIM-G-002</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>tau=exp(-tL) candidate realization of PRIM-G-002 falsified (violates its own Liouville-condition definition, 9/9 families)</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>any graph with &gt;=1 edge</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>det(exp(-tL))=exp(-t*trace L) -&gt; 0 as t-&gt;inf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22568,7 +23209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23235,47 +23876,111 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>tau realized as diffusion semigroup exp(-tL)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>N/A -- ruled out as a candidate realization of tau</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NO-GO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17: violates tau's own Liouville-condition definition on 9/9 benchmark families (FALS-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Delta realized as I-P_ker(L) endomorphism, composed as kappa o tau o Delta</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>N/A -- ruled out</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NO-GO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17: composition degenerates to the identically-zero map on 9/9 families (FALS-002)</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Critical frontier (per closure layer)</t>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gamma_graph (graph-spectral realization) conjugate to exp(-hL) via orthogonal transform</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>A different conjugacy criterion or realization, if one exists</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NO-GO (for tested criterion)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17: no near-conjugacy found on 9/9 families, Procrustes residuals 0.88-0.97 (FALS-003)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>Open_Questions</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>Closure_Criterion</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>Frontier_Status</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>Execution_Rule</t>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Delta reconstructible from tau(automorphism)+kappa(spectrum) alone</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>N/A -- ruled out by external theorem</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NO-GO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17: cospectral non-isomorphic graphs are a standard counterexample (FALS-004, EXT-002)</t>
         </is>
       </c>
     </row>
@@ -23287,207 +23992,93 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Primitive &amp; grammar reconciliation</t>
+          <t>Common minimal grammar Gamma_min across all 4 registered primitive systems (A,B,C,D)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Relation among Δ,τ,κ,Π and competing grammar realizations</t>
+          <t>A tested structure-preserving embedding from each of A,B,C,D into a single candidate</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Equivalence/hierarchy/embedding/irreducible extension</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Canonical grammar relation with no hidden primitive</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Identify parent prerequisites before calculation; preserve all downstream calculated results.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Organizational / fixed-point closure</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Γ:X→X and organizational closure</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Existence, convergence, least fixed point, attractor uniqueness, relation to R</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Explicit theorem with hypotheses</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Identify parent prerequisites before calculation; preserve all downstream calculated results.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Persistence &amp; spectral closure</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Π_O and λ_c</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Derive Π_O and threshold from dynamics</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Derived functional + unique/controlled threshold where claimed</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Identify parent prerequisites before calculation; preserve all downstream calculated results.</t>
+          <t>PRF-PRIM-EXEC-2026-08-17: not established; closest result is a 3-slot reduction WITHIN grammar A/D alone (Delta,tau-slot,kappa), not a 4-grammar unification. See Common_Grammar sheet, results/workbooks/C0_PRF_PRIM_Primitive_Reconciliation.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Spectral→geometry→Lorentzian</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>L→Δ_g→K_g→d_g→g and Lorentzian signature</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Universal continuum class; Lorentzian emergence</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Continuum Lorentzian metric derived under stated hypotheses</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Identify parent prerequisites before calculation; preserve all downstream calculated results.</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Critical frontier (per closure layer)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Nature spectrum &amp; constants</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Nature-spectrum correspondence and dimensional constants</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Spec correspondence; c,ħ,G,e classifications; C_UOC</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Internal derivation or explicit empirical admission</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Identify parent prerequisites before calculation; preserve all downstream calculated results.</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>Open_Questions</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>Closure_Criterion</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>Frontier_Status</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>Execution_Rule</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gauge/representation/matter/generation</t>
+          <t>Primitive &amp; grammar reconciliation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Full particle/gauge sector</t>
+          <t>Relation among Δ,τ,κ,Π and competing grammar realizations</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Gauge group, reps, 3 generations, mass hierarchy, neutrinos</t>
+          <t>Equivalence/hierarchy/embedding/irreducible extension</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Predictive matter sector with correct symmetries</t>
+          <t>Canonical grammar relation with no hidden primitive</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -23504,27 +24095,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Quantum closure</t>
+          <t>Organizational / fixed-point closure</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Quantum theory integrated with persistence/geometry</t>
+          <t>Γ:X→X and organizational closure</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Born rule, quantum geometry/gravity integration</t>
+          <t>Existence, convergence, least fixed point, attractor uniqueness, relation to R</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Consistent quantum + semiclassical limits</t>
+          <t>Explicit theorem with hypotheses</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -23541,27 +24132,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cosmological/horizon/information</t>
+          <t>Persistence &amp; spectral closure</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scale→horizon→information→cutoff→cosmology</t>
+          <t>Π_O and λ_c</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Scale anchor, P_H, information normalization, non-circular Xi</t>
+          <t>Derive Π_O and threshold from dynamics</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>All upstream links independently generated</t>
+          <t>Derived functional + unique/controlled threshold where claimed</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -23578,27 +24169,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Biological/adaptive</t>
+          <t>Spectral→geometry→Lorentzian</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Biology reverse-derived from common kernel</t>
+          <t>L→Δ_g→K_g→d_g→g and Lorentzian signature</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Replication, heredity, selection, adaptation, fitness</t>
+          <t>Universal continuum class; Lorentzian emergence</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>No extra primitive or explicit necessary extension</t>
+          <t>Continuum Lorentzian metric derived under stated hypotheses</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -23615,27 +24206,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Compiler closure</t>
+          <t>Nature spectrum &amp; constants</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Universal executable representation</t>
+          <t>Nature-spectrum correspondence and dimensional constants</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Normal form, confluence, routing, runtime, backends, completeness</t>
+          <t>Spec correspondence; c,ħ,G,e classifications; C_UOC</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Executable independently testable compiler</t>
+          <t>Internal derivation or explicit empirical admission</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -23652,27 +24243,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Validation/falsification</t>
+          <t>Gauge/representation/matter/generation</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cross-domain recovery and novel predictions</t>
+          <t>Full particle/gauge sector</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Full suite, numerical reproducibility, falsification</t>
+          <t>Gauge group, reps, 3 generations, mass hierarchy, neutrinos</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Independent reproduction + surviving empirical tests</t>
+          <t>Predictive matter sector with correct symmetries</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -23686,270 +24277,320 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Quantum closure</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Quantum theory integrated with persistence/geometry</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Born rule, quantum geometry/gravity integration</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Consistent quantum + semiclassical limits</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Identify parent prerequisites before calculation; preserve all downstream calculated results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Cosmological/horizon/information</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Scale→horizon→information→cutoff→cosmology</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Scale anchor, P_H, information normalization, non-circular Xi</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>All upstream links independently generated</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Identify parent prerequisites before calculation; preserve all downstream calculated results.</t>
+        </is>
+      </c>
+    </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Phase execution plan (priority queue)</t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Biological/adaptive</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Biology reverse-derived from common kernel</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Replication, heredity, selection, adaptation, fitness</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>No extra primitive or explicit necessary extension</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Identify parent prerequisites before calculation; preserve all downstream calculated results.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>Phase</t>
-        </is>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>Program</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>Closure_Layer</t>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Compiler closure</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Universal executable representation</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Normal form, confluence, routing, runtime, backends, completeness</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Executable independently testable compiler</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Identify parent prerequisites before calculation; preserve all downstream calculated results.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Source synchronization</t>
+          <t>Validation/falsification</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>All source corpus + registries synchronized</t>
+          <t>Cross-domain recovery and novel predictions</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full suite, numerical reproducibility, falsification</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>v3 database + current chat</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Canonical ontology</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Primitive/grammar reconciliation</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>OPEN THEOREM</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>C0</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Organizational closure</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Fixed points / attractors / compiler closure</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>OPEN THEOREM</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>C1</t>
+          <t>Independent reproduction + surviving empirical tests</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Identify parent prerequisites before calculation; preserve all downstream calculated results.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Spectral/persistence</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Persistence functional + threshold</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>PARTIAL/OPEN</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>C2</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Phase execution plan (priority queue)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Geometry/Lorentzian</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Continuum geometry + Lorentzian emergence</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>PARTIAL/OPEN</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>C3</t>
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>Closure_Layer</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nature/constants</t>
+          <t>Source synchronization</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Constant generation + absolute scale</t>
+          <t>All source corpus + registries synchronized</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>v3 database + current chat</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gauge/matter</t>
+          <t>Canonical ontology</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Group, reps, generations, masses, couplings</t>
+          <t>Primitive/grammar reconciliation</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PARTIAL/OPEN</t>
+          <t>OPEN THEOREM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Organizational closure</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Certified recovery + quantum geometry integration</t>
+          <t>Fixed points / attractors / compiler closure</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PARTIAL/OPEN</t>
+          <t>OPEN THEOREM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cosmology</t>
+          <t>Spectral/persistence</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scale + horizon + information closure; downstream relations preserved</t>
+          <t>Persistence functional + threshold</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -23959,51 +24600,51 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Geometry/Lorentzian</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Reverse organizational recovery</t>
+          <t>Continuum geometry + Lorentzian emergence</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PARTIAL/OPEN</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Compiler</t>
+          <t>Nature/constants</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Executable UOC runtime and backends</t>
+          <t>Constant generation + absolute scale</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -24013,32 +24654,167 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Gauge/matter</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Group, reps, generations, masses, couplings</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PARTIAL/OPEN</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Certified recovery + quantum geometry integration</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PARTIAL/OPEN</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Scale + horizon + information closure; downstream relations preserved</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PARTIAL/OPEN</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Reverse organizational recovery</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Compiler</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Executable UOC runtime and backends</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Validation/falsification</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Cross-domain recovery, invariance, numerical and empirical tests</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>PARTIAL/OPEN</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
@@ -39642,17 +40418,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13.5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="28.8" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="47.7" customWidth="1" min="5" max="5"/>
-    <col width="32.4" customWidth="1" min="6" max="6"/>
-    <col width="19.8" customWidth="1" min="7" max="7"/>
-    <col width="34.2" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -47002,6 +47778,90 @@
       <c r="H175" t="inlineStr">
         <is>
           <t>SOURCE-CODED; see closure/status layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>EQ-PRF-PRIM-001</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>L = Inc * Inc^T</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Graph Laplacian as Gram matrix of the discrete gradient (incidence operator)</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>EXT-001 (Godsil &amp; Royle, Algebraic Graph Theory Ch.13)</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>PROVEN + verified exact on 9/9 families in PRF-PRIM-EXEC-2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>EQ-PRF-PRIM-002</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>det(exp(-tL)) = exp(-t*trace(L)) = exp(-2t|E|)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Determinant of the diffusion semigroup -- shows exp(-tL) is NOT volume-preserving for any graph with an edge</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>PRF-PRIM-EXEC-2026-08-17 (derived while testing tau candidate realizations)</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>PROVEN + verified exact on 9/9 families; falsifies tau=exp(-tL) under PRIM-G-002's Liouville-condition definition</t>
         </is>
       </c>
     </row>
@@ -47016,13 +47876,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.5" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="21.6" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="23.4" customWidth="1" min="3" max="3"/>
+    <col width="16.2" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -48345,6 +49205,28 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DER-C0-PRIMGRAPH-001</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Graph-spectral realization test of {Delta,tau,kappa,Pi} against PRF-PRIM (kappa=P_ker(L) idempotent+commutes with automorphism tau; Pi=ker(L) derivable; tau=exp(-tL) FALSIFIED; Delta type-mismatch found)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PRF-PRIM, DER-SPC-002..005</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CALCULATED/PARTIAL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
